--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-04-2026.xlsx
@@ -571,29 +571,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -689,29 +689,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -807,29 +807,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -925,29 +925,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -1043,29 +1043,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -1161,29 +1161,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -1279,29 +1279,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -1397,29 +1397,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -1515,29 +1515,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -1633,29 +1633,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -1751,29 +1751,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -1869,29 +1869,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -1987,29 +1987,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -2105,29 +2105,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -2223,29 +2223,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -2433,29 +2433,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -2551,29 +2551,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -2669,29 +2669,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -2787,29 +2787,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>£79.58</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£51.23</t>
+          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Max retries exceeded with url: /725mm-celotex-pl4060-pir-insulated-plasterboard---12m-x-24m-2336-p.asp (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x00000253C3942190&gt;, 'Connection to onlineinsulation-sales.com timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2905,29 +2905,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -3023,29 +3023,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -3141,29 +3141,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -3259,29 +3259,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -3377,29 +3377,29 @@
           <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (374, 409). Other element would receive the click: &lt;div class="text_106265619"&gt;...&lt;/div&gt;
   (Session info: chrome=146.0.7680.178)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6833229c5+2ed785]
-	chromedriver!GetHandleVerifier [0x7ff68304a0d0+14e90]
-	chromedriver!(No symbol) [0x7ff682dadb2d]
-	chromedriver!(No symbol) [0x7ff682e0f0e5]
-	chromedriver!(No symbol) [0x7ff682e0c7fa]
-	chromedriver!(No symbol) [0x7ff682e09685]
-	chromedriver!(No symbol) [0x7ff682e08537]
-	chromedriver!(No symbol) [0x7ff682dfb186]
-	chromedriver!(No symbol) [0x7ff682e2ff8a]
-	chromedriver!(No symbol) [0x7ff682dfaa06]
-	chromedriver!(No symbol) [0x7ff682e53b9b]
-	chromedriver!(No symbol) [0x7ff682df9298]
-	chromedriver!(No symbol) [0x7ff682dfa183]
-	chromedriver!GetHandleVerifier [0x7ff68334de0d+318bcd]
-	chromedriver!GetHandleVerifier [0x7ff683348588+313348]
-	chromedriver!GetHandleVerifier [0x7ff683369d7a+334b3a]
-	chromedriver!GetHandleVerifier [0x7ff683066785+31545]
-	chromedriver!GetHandleVerifier [0x7ff68306facc+3a88c]
-	chromedriver!GetHandleVerifier [0x7ff683053634+1e3f4]
-	chromedriver!GetHandleVerifier [0x7ff6830537e6+1e5a6]
-	chromedriver!GetHandleVerifier [0x7ff683037e37+2bf7]
-	KERNEL32!BaseThreadInitThunk [0x7ffc67b2e8d7+17]
-	ntdll!RtlUserThreadStart [0x7ffc68bec48c+2c]
+	chromedriver!GetHandleVerifier [0x7ff7c91a29c5+2ed785]
+	chromedriver!GetHandleVerifier [0x7ff7c8eca0d0+14e90]
+	chromedriver!(No symbol) [0x7ff7c8c2db2d]
+	chromedriver!(No symbol) [0x7ff7c8c8f0e5]
+	chromedriver!(No symbol) [0x7ff7c8c8c7fa]
+	chromedriver!(No symbol) [0x7ff7c8c89685]
+	chromedriver!(No symbol) [0x7ff7c8c88537]
+	chromedriver!(No symbol) [0x7ff7c8c7b186]
+	chromedriver!(No symbol) [0x7ff7c8caff8a]
+	chromedriver!(No symbol) [0x7ff7c8c7aa06]
+	chromedriver!(No symbol) [0x7ff7c8cd3b9b]
+	chromedriver!(No symbol) [0x7ff7c8c79298]
+	chromedriver!(No symbol) [0x7ff7c8c7a183]
+	chromedriver!GetHandleVerifier [0x7ff7c91cde0d+318bcd]
+	chromedriver!GetHandleVerifier [0x7ff7c91c8588+313348]
+	chromedriver!GetHandleVerifier [0x7ff7c91e9d7a+334b3a]
+	chromedriver!GetHandleVerifier [0x7ff7c8ee6785+31545]
+	chromedriver!GetHandleVerifier [0x7ff7c8eefacc+3a88c]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed3634+1e3f4]
+	chromedriver!GetHandleVerifier [0x7ff7c8ed37e6+1e5a6]
+	chromedriver!GetHandleVerifier [0x7ff7c8eb7e37+2bf7]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f2f7e8d7+17]
+	ntdll!RtlUserThreadStart [0x7ff9f3acc48c+2c]
 </t>
         </is>
       </c>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£1790.88</t>
         </is>
       </c>
     </row>
